--- a/output/Data and Chart Outputs/japan_power_prices_daily.xlsx
+++ b/output/Data and Chart Outputs/japan_power_prices_daily.xlsx
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -799,41 +799,6 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
-        <is>
-          <t>FY2021: http 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FY2022: http 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FY2023: http 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FY2024: http 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FY2025: http 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
         <is>
           <t>FY2026: http 200</t>
         </is>
